--- a/复制演示--目标文件.xlsx
+++ b/复制演示--目标文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10192" windowHeight="9090"/>
+    <workbookView windowWidth="22192" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="目标" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>花名册</t>
   </si>
   <si>
-    <t>姓名</t>
+    <t>姓 名</t>
+  </si>
+  <si>
+    <t>性  别</t>
+  </si>
+  <si>
+    <t>出生时间</t>
+  </si>
+  <si>
+    <t>民  族</t>
   </si>
   <si>
     <t>入职时间</t>
@@ -1024,10 +1033,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,8 +1049,11 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1071,11 +1083,20 @@
       </c>
       <c r="J2" t="s">
         <v>10</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
